--- a/forms/trg/Formulir_TRG_hortibb.xlsx
+++ b/forms/trg/Formulir_TRG_hortibb.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Katriani Mantja</t>
+          <t>Prof. Muh. Farid BDR</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Horticulture</t>
+          <t>Plant Breeding</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6522-1689</t>
+          <t>0000-0002-7178-7790</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6016007</t>
+          <t>6022499</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57205103120</t>
+          <t>57202443204</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Nuniek Widiayani, SP. MP.</t>
+          <t>Dr. Katriani Mantja</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Crop Science</t>
+          <t>Horticulture</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1207-7737</t>
+          <t>0000-0001-6522-1689</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6041474</t>
+          <t>6016007</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57210918296</t>
+          <t>57205103120</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,22 +1007,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>DR. Nurul Amalina Mohd Zain</t>
+          <t>Nuniek Widiayani, SP. MP.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Universiti Malaysia, Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Plant Stress Physiology</t>
+          <t>Crop Science</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,13 +1031,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5764-2715</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
+          <t>0000-0003-1207-7737</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6041474</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>56388629900</t>
+          <t>57210918296</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1056,31 +1056,39 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. Bunyamin Taran, PhD</t>
+          <t>DR. Nurul Amalina Mohd Zain</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>University of Saskatchewan, Kanada</t>
+          <t>Universiti Malaysia, Malaysia</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Plant Breeding and Genetic</t>
+          <t>Plant Stress Physiology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-5764-2715</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>56388629900</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1093,22 +1101,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Okon Odiong Unung</t>
+          <t>Prof. Ir. Bunyamin Taran, PhD</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>National Biotecnology Research and Development Agency, Nigeria</t>
+          <t>University of Saskatchewan, Kanada</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Plant Breeding and Biotecnology</t>
+          <t>Plant Breeding and Genetic</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1130,22 +1138,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Wang Juan</t>
+          <t>Dr. Okon Odiong Unung</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Maize Research Institute-Shandong Academy of Agricultural Science</t>
+          <t>National Biotecnology Research and Development Agency, Nigeria</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Plant Breeding and Genetic</t>
+          <t>Plant Breeding and Biotecnology</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1167,43 +1175,31 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Rusnadi Padjung</t>
+          <t>Wang Juan</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Maize Research Institute-Shandong Academy of Agricultural Science</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Crop Production</t>
+          <t>Plant Breeding and Genetic</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-8644-3210</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>6005400</t>
-        </is>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>36437407200</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1216,12 +1212,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Fuad Anshori</t>
+          <t>Prof. Rusnadi Padjung</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1231,7 +1227,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Plant Breeding and Biotechnology</t>
+          <t>Crop Production</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1240,17 +1236,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8275-0179</t>
+          <t>0000-0002-8644-3210</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>6781240</t>
+          <t>6005400</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57205296661</t>
+          <t>36437407200</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1265,12 +1261,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Rahmansyah Dermawan</t>
+          <t>Dr. Muhammad Fuad Anshori</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1280,7 +1276,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Horticulture</t>
+          <t>Plant Breeding and Biotechnology</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1289,17 +1285,17 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4206-5673</t>
+          <t>0000-0001-8275-0179</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>6005104</t>
+          <t>6781240</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57202441198</t>
+          <t>57205296661</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1314,12 +1310,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ifayanti Ridwan Saleh</t>
+          <t>Dr. Rahmansyah Dermawan</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1329,7 +1325,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Plant Ecophysiology</t>
+          <t>Horticulture</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1338,17 +1334,17 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9528-3151</t>
+          <t>0000-0003-4206-5673</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>6016263</t>
+          <t>6005104</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>57218717855</t>
+          <t>57202441198</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1363,22 +1359,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Sitti Inderiati</t>
+          <t>Dr. Ifayanti Ridwan Saleh</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Politeknik Pertanian Pangkep</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Tissue Culture</t>
+          <t>Plant Ecophysiology</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1387,17 +1383,17 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7367-408X</t>
+          <t>0000-0001-9528-3151</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>6042003</t>
+          <t>6016263</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>58561725700</t>
+          <t>57218717855</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1412,22 +1408,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>A. Chamsitasari Zulfikarahmi A. Jamil</t>
+          <t>Sitti Inderiati</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Politeknik Pertanian Pangkep</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Plant Breeding</t>
+          <t>Tissue Culture</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1436,11 +1432,19 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>my-orcid?orcid=0009-0003-5834-6020</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
+          <t>0000-0001-7367-408X</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>6042003</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>58561725700</t>
+        </is>
+      </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1453,12 +1457,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>M. Alfan Ikhlasul Amal</t>
+          <t>A. Chamsitasari Zulfikarahmi A. Jamil</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1477,7 +1481,7 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0009-0008-2372-7428</t>
+          <t>my-orcid?orcid=0009-0003-5834-6020</t>
         </is>
       </c>
       <c r="K17" s="12" t="n"/>
@@ -1492,18 +1496,42 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>M. Alfan Ikhlasul Amal</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Plant Breeding</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-2372-7428</t>
+        </is>
+      </c>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1692,15 +1720,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
